--- a/output/details/2026-06-04/preprocessed_data.xlsx
+++ b/output/details/2026-06-04/preprocessed_data.xlsx
@@ -15231,25 +15231,25 @@
         <v>46177</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.1197183925118326</v>
+        <v>-0.1275705593894225</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1278182096696195</v>
+        <v>-0.1504705196643501</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1276504104665735</v>
+        <v>-0.1501798749992121</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1134613649956459</v>
+        <v>-0.002172367649801933</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001694387352614553</v>
+        <v>0.001688336128672833</v>
       </c>
       <c r="G2" t="n">
-        <v>2.011950964765778</v>
+        <v>2.584685308690809</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.426809701111237</v>
+        <v>-0.2664350242095723</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
